--- a/data/trans_orig/P04B3_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63875</t>
+          <t>63695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>95059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47713</t>
+          <t>47982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73278</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118504</t>
+          <t>118862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160076</t>
+          <t>159822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62818</t>
+          <t>62023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96596</t>
+          <t>94886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40306</t>
+          <t>39484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62195</t>
+          <t>61684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108488</t>
+          <t>109282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>151069</t>
+          <t>150911</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86330</t>
+          <t>89634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125895</t>
+          <t>126835</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99191</t>
+          <t>99206</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>168744</t>
+          <t>167456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215018</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>219342</t>
+          <t>220061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268194</t>
+          <t>268186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>233674</t>
+          <t>233245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>269380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>463492</t>
+          <t>465927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>524452</t>
+          <t>523314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53989</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81538</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>55455</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81224</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>114970</t>
+          <t>113619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>154784</t>
+          <t>153483</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55016</t>
+          <t>54444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87490</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43463</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>66590</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104687</t>
+          <t>105279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145420</t>
+          <t>142759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>73694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108917</t>
+          <t>110484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64672</t>
+          <t>65740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92370</t>
+          <t>92226</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145469</t>
+          <t>145160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191263</t>
+          <t>190250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,79%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202786</t>
+          <t>201955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>248134</t>
+          <t>245323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167462</t>
+          <t>167763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202336</t>
+          <t>200346</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>381167</t>
+          <t>382668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>437528</t>
+          <t>439680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29440</t>
+          <t>29856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129883</t>
+          <t>131416</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23959</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>50803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162858</t>
+          <t>163181</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22635</t>
+          <t>28268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118772</t>
+          <t>121473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>35563</t>
+          <t>40198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>136485</t>
+          <t>134984</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28029</t>
+          <t>29170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129422</t>
+          <t>131428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>22625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38540</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41304</t>
+          <t>41602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158903</t>
+          <t>156878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>302492</t>
+          <t>298406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>580967</t>
+          <t>580149</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74618</t>
+          <t>74382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94738</t>
+          <t>94854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>388537</t>
+          <t>389425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>710972</t>
+          <t>697123</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>173595</t>
+          <t>174335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224386</t>
+          <t>222444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139395</t>
+          <t>137762</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>207555</t>
+          <t>218773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>349191</t>
+          <t>348054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>108418</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157272</t>
+          <t>154674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54568</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142579</t>
+          <t>144077</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>164675</t>
+          <t>172379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>279486</t>
+          <t>281223</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>190118</t>
+          <t>189323</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>251188</t>
+          <t>252255</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60288</t>
+          <t>68602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>177672</t>
+          <t>179455</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>234137</t>
+          <t>250865</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>407534</t>
+          <t>406812</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>451243</t>
+          <t>455328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522091</t>
+          <t>524499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>530314</t>
+          <t>528559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>809129</t>
+          <t>805018</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1001069</t>
+          <t>1002553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1406723</t>
+          <t>1373181</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>93530</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131239</t>
+          <t>131171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>173393</t>
+          <t>171947</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>396201</t>
+          <t>396228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279394</t>
+          <t>286103</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>514393</t>
+          <t>503117</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51789</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81674</t>
+          <t>79643</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93522</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150114</t>
+          <t>146805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150193</t>
+          <t>155509</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>216836</t>
+          <t>215837</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>66544</t>
+          <t>67951</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102123</t>
+          <t>102882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101833</t>
+          <t>102220</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>160304</t>
+          <t>159985</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181741</t>
+          <t>180964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>250561</t>
+          <t>250989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>192380</t>
+          <t>192792</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>238443</t>
+          <t>237736</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>255609</t>
+          <t>263988</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>399456</t>
+          <t>400763</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>475946</t>
+          <t>465762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>618736</t>
+          <t>615155</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>33051</t>
+          <t>31886</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>71400</t>
+          <t>69286</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>160783</t>
+          <t>161864</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>204078</t>
+          <t>204258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>205718</t>
+          <t>204003</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>264919</t>
+          <t>260062</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12662</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>40912</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84313</t>
+          <t>83712</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>115859</t>
+          <t>116680</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103914</t>
+          <t>103415</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142804</t>
+          <t>146907</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>59220</t>
+          <t>61207</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>119738</t>
+          <t>119287</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162105</t>
+          <t>162241</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>152708</t>
+          <t>149579</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>210428</t>
+          <t>207257</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>104892</t>
+          <t>102460</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>156744</t>
+          <t>156593</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>312855</t>
+          <t>313620</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>368608</t>
+          <t>365225</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>433560</t>
+          <t>432350</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>506930</t>
+          <t>509937</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>462698</t>
+          <t>433316</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>642865</t>
+          <t>646518</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>575433</t>
+          <t>575553</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>868179</t>
+          <t>860686</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1107349</t>
+          <t>1107844</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1452235</t>
+          <t>1435652</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>342705</t>
+          <t>328601</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>494219</t>
+          <t>490054</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>379718</t>
+          <t>363228</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>508611</t>
+          <t>503304</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>768992</t>
+          <t>773297</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>972878</t>
+          <t>975846</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>477797</t>
+          <t>466910</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>681329</t>
+          <t>678776</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>493831</t>
+          <t>483600</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>662847</t>
+          <t>662628</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1046743</t>
+          <t>1046416</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1315550</t>
+          <t>1316416</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1597307</t>
+          <t>1596852</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2101423</t>
+          <t>2160134</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1693386</t>
+          <t>1690548</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2170253</t>
+          <t>2139761</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3346591</t>
+          <t>3349402</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4024302</t>
+          <t>4028027</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>79019</t>
+          <t>88058</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63695</t>
+          <t>72681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95059</t>
+          <t>107946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59859</t>
+          <t>68083</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47982</t>
+          <t>54260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71841</t>
+          <t>82126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>138878</t>
+          <t>156141</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118862</t>
+          <t>137029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>159822</t>
+          <t>182199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>85044</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62023</t>
+          <t>68123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94886</t>
+          <t>105204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39484</t>
+          <t>47175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61684</t>
+          <t>70999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>127640</t>
+          <t>143701</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109282</t>
+          <t>124311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150911</t>
+          <t>167619</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106040</t>
+          <t>118421</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89634</t>
+          <t>98693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126835</t>
+          <t>139648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>79649</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99206</t>
+          <t>109597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>190425</t>
+          <t>212446</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167456</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214643</t>
+          <t>240318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>242322</t>
+          <t>259095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>220061</t>
+          <t>235073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268186</t>
+          <t>283353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>252684</t>
+          <t>266898</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>233245</t>
+          <t>247605</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>269380</t>
+          <t>283649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>495006</t>
+          <t>525994</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>465927</t>
+          <t>494632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>523314</t>
+          <t>558969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>951950</t>
+          <t>1038283</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951950</t>
+          <t>1038283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>951950</t>
+          <t>1038283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67667</t>
+          <t>76074</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53904</t>
+          <t>61727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>93452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66382</t>
+          <t>72428</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55455</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79996</t>
+          <t>87249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>134049</t>
+          <t>148502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113619</t>
+          <t>126681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153483</t>
+          <t>170501</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69023</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54444</t>
+          <t>59370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85720</t>
+          <t>93095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53924</t>
+          <t>62454</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43799</t>
+          <t>50548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66590</t>
+          <t>75487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>122947</t>
+          <t>136576</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105279</t>
+          <t>118670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>142759</t>
+          <t>160203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90211</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73694</t>
+          <t>78430</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110484</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>89836</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65740</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92226</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>167744</t>
+          <t>187437</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145160</t>
+          <t>166107</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190250</t>
+          <t>212527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>225312</t>
+          <t>235415</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>201955</t>
+          <t>211963</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>245323</t>
+          <t>256501</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184741</t>
+          <t>198425</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167763</t>
+          <t>180764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200346</t>
+          <t>215948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>410053</t>
+          <t>433840</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>382668</t>
+          <t>405191</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>439680</t>
+          <t>463194</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78417</t>
+          <t>86897</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29856</t>
+          <t>72243</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131416</t>
+          <t>103839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>26461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40530</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>110078</t>
+          <t>121935</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50803</t>
+          <t>103802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163181</t>
+          <t>141862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -1976,102 +1976,102 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>71605</t>
+          <t>77833</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28268</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121473</t>
+          <t>93543</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>19,83%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>23412</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17259</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>31458</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>16,84%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>101245</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>85299</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>119710</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>18,18%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>20315</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>14385</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27528</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>91919</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>40198</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>134984</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>4,82%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77324</t>
+          <t>84759</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>67671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131428</t>
+          <t>101368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29685</t>
+          <t>35035</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22625</t>
+          <t>26435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37810</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107008</t>
+          <t>119794</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41602</t>
+          <t>101186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>156878</t>
+          <t>139386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>440918</t>
+          <t>222122</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>298406</t>
+          <t>200662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>580149</t>
+          <t>245642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>84595</t>
+          <t>93306</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74382</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94854</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>525514</t>
+          <t>315429</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>389425</t>
+          <t>291452</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>697123</t>
+          <t>342051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>228444</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174335</t>
+          <t>202601</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>222444</t>
+          <t>258289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>104115</t>
+          <t>124636</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>107537</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>137762</t>
+          <t>145907</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>300954</t>
+          <t>353080</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>218773</t>
+          <t>319095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348054</t>
+          <t>388548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>131868</t>
+          <t>147162</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108418</t>
+          <t>123604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>154674</t>
+          <t>176390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>108699</t>
+          <t>121755</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52173</t>
+          <t>104044</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>144077</t>
+          <t>138795</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>240566</t>
+          <t>268917</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172379</t>
+          <t>240747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281223</t>
+          <t>301419</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>216659</t>
+          <t>231873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>189323</t>
+          <t>203004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>252255</t>
+          <t>262128</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>135206</t>
+          <t>152200</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68602</t>
+          <t>131253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>179455</t>
+          <t>171397</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>351865</t>
+          <t>384073</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>250865</t>
+          <t>350873</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>406812</t>
+          <t>424249</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>489453</t>
+          <t>524364</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>455328</t>
+          <t>491320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524499</t>
+          <t>560710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>629267</t>
+          <t>460960</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>528559</t>
+          <t>436275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>805018</t>
+          <t>488131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1118720</t>
+          <t>985325</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1002553</t>
+          <t>940517</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1373181</t>
+          <t>1029175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977287</t>
+          <t>859552</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012106</t>
+          <t>1991395</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012106</t>
+          <t>1991395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012106</t>
+          <t>1991395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>111418</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94434</t>
+          <t>121162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131171</t>
+          <t>165417</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>235382</t>
+          <t>195889</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171947</t>
+          <t>176415</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>396228</t>
+          <t>220345</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>346800</t>
+          <t>337922</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>286103</t>
+          <t>307846</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>503117</t>
+          <t>369428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>64775</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50972</t>
+          <t>60354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>79643</t>
+          <t>92506</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>124335</t>
+          <t>136536</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93689</t>
+          <t>118874</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146805</t>
+          <t>155389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>189110</t>
+          <t>211729</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>186129</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>215837</t>
+          <t>236530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>83013</t>
+          <t>97128</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>67951</t>
+          <t>77851</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>102882</t>
+          <t>115241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>136874</t>
+          <t>159935</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102220</t>
+          <t>141611</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159985</t>
+          <t>178873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>219887</t>
+          <t>257063</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>180964</t>
+          <t>231374</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>250989</t>
+          <t>288141</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>215839</t>
+          <t>253610</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>192792</t>
+          <t>227640</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>237736</t>
+          <t>280191</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>343964</t>
+          <t>337090</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>263988</t>
+          <t>312824</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>400763</t>
+          <t>362153</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>559803</t>
+          <t>590700</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>465762</t>
+          <t>551854</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>615155</t>
+          <t>623621</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>840554</t>
+          <t>829450</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>840554</t>
+          <t>829450</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840554</t>
+          <t>829450</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1315600</t>
+          <t>1397414</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1315600</t>
+          <t>1397414</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1315600</t>
+          <t>1397414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>48950</t>
+          <t>57298</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>39448</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>69286</t>
+          <t>79661</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>181945</t>
+          <t>212899</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>161864</t>
+          <t>188685</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>204258</t>
+          <t>238813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>230895</t>
+          <t>270197</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>204003</t>
+          <t>241585</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>260062</t>
+          <t>302879</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22674</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12280</t>
+          <t>14901</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40912</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>99822</t>
+          <t>116837</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83712</t>
+          <t>98282</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116680</t>
+          <t>135125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>122497</t>
+          <t>143620</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>103415</t>
+          <t>123035</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>146907</t>
+          <t>168714</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>37452</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>21265</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>61207</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>140044</t>
+          <t>153093</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>119287</t>
+          <t>132629</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162241</t>
+          <t>177578</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>177496</t>
+          <t>189499</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>149579</t>
+          <t>160316</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>207257</t>
+          <t>218060</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>131266</t>
+          <t>115097</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>102460</t>
+          <t>89661</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>156593</t>
+          <t>138885</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>339560</t>
+          <t>361453</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>313620</t>
+          <t>334749</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>365225</t>
+          <t>391868</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>470825</t>
+          <t>476550</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>432350</t>
+          <t>441081</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>509937</t>
+          <t>518537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>582311</t>
+          <t>678805</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>433316</t>
+          <t>628320</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>646518</t>
+          <t>724387</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>679344</t>
+          <t>708973</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>575553</t>
+          <t>668804</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>860686</t>
+          <t>752665</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1261655</t>
+          <t>1387778</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1107844</t>
+          <t>1323995</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1435652</t>
+          <t>1456117</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>437775</t>
+          <t>486137</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>328601</t>
+          <t>445966</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>490054</t>
+          <t>531659</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>456904</t>
+          <t>519651</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>363228</t>
+          <t>481549</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>503304</t>
+          <t>557544</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>894679</t>
+          <t>1005788</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>773297</t>
+          <t>948854</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>975846</t>
+          <t>1063845</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>610699</t>
+          <t>666188</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>466910</t>
+          <t>618362</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>678776</t>
+          <t>717470</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>603726</t>
+          <t>684124</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>483600</t>
+          <t>643533</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>662628</t>
+          <t>727450</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1214425</t>
+          <t>1350312</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1046416</t>
+          <t>1287206</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1316416</t>
+          <t>1425094</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1745111</t>
+          <t>1609703</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1596852</t>
+          <t>1548579</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2160134</t>
+          <t>1674249</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1834811</t>
+          <t>1718133</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1690548</t>
+          <t>1671991</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2139761</t>
+          <t>1772391</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3579922</t>
+          <t>3327836</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3349402</t>
+          <t>3247417</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4028027</t>
+          <t>3411726</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3375896</t>
+          <t>3440833</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3375896</t>
+          <t>3440833</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3375896</t>
+          <t>3440833</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3574785</t>
+          <t>3630881</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3574785</t>
+          <t>3630881</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3574785</t>
+          <t>3630881</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6950681</t>
+          <t>7071714</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6950681</t>
+          <t>7071714</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6950681</t>
+          <t>7071714</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
